--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -16150,13 +16150,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27144F54-D84F-4CFF-9961-A9C66A0F29A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E20D03E-985C-4843-BC78-FED954F53172}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFEC99F6-855E-407A-9FBB-28B247F25C50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2ABEDFD-73DF-4B78-BA57-A1F71354FAF3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EC59C5-7A31-4481-A104-86511D088148}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D321F855-1264-4DA1-A373-F96152157721}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -16150,13 +16150,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E20D03E-985C-4843-BC78-FED954F53172}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B7E31EE-726A-4696-9060-4BE4534F4200}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2ABEDFD-73DF-4B78-BA57-A1F71354FAF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF03CC12-C907-4ADC-B416-8CD4490952B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D321F855-1264-4DA1-A373-F96152157721}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22E407F2-5C2F-4D2B-A342-AF764C14FD2D}"/>
 </file>
--- a/Geral_Poupanca.xlsx
+++ b/Geral_Poupanca.xlsx
@@ -43605,13 +43605,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCB47FEA-236B-48EE-BB52-A6ED78B74780}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01D7E660-26EA-4D3F-A136-477D6C68A376}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D074A41-0A51-420B-A2C0-D06F0FC9041A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F89625A3-2CEE-4F99-ADAE-C8C37AEFF9C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D80563A2-9C6C-46A9-A61A-9474E08E66B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4415CB95-CC52-493B-8466-B91D9D3A8D4E}"/>
 </file>